--- a/协作/34-事故与复盘记录.xlsx
+++ b/协作/34-事故与复盘记录.xlsx
@@ -630,10 +630,10 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation sqref="C2:C121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="C2:C121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="只能选择下拉里的值" type="list">
+    <dataValidation sqref="M2:M121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"开放,已关闭"</formula1>
     </dataValidation>
   </dataValidations>
